--- a/literature_review/literature_review2025.xlsx
+++ b/literature_review/literature_review2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10105"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melinaleite/github/dispersionTest/literature_review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678E5A39-1CB1-C742-ACD4-081964448914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1623FEF7-6800-A947-89E7-A818117CBF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="7720" windowWidth="28800" windowHeight="10280" xr2:uid="{FF01F566-405A-2E41-802A-92292ABA15DA}"/>
+    <workbookView xWindow="0" yWindow="2420" windowWidth="36760" windowHeight="15580" xr2:uid="{FF01F566-405A-2E41-802A-92292ABA15DA}"/>
   </bookViews>
   <sheets>
     <sheet name="literature_review2025" sheetId="1" r:id="rId1"/>
@@ -4612,8 +4612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B8D15F-4FE6-BE4B-97F4-E8728CDE7A9F}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AM214"/>
+  <dimension ref="A1:AM201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="10.83203125" hidden="1" customWidth="1"/>
@@ -4624,7 +4623,7 @@
     <col min="31" max="31" width="10.83203125" style="2"/>
     <col min="32" max="32" width="47.1640625" customWidth="1"/>
     <col min="33" max="36" width="10.83203125" style="2"/>
-    <col min="37" max="37" width="18.6640625" style="2" customWidth="1"/>
+    <col min="37" max="37" width="47.5" style="2" customWidth="1"/>
     <col min="38" max="38" width="78" style="7" customWidth="1"/>
     <col min="39" max="39" width="63.33203125" style="8" customWidth="1"/>
   </cols>
@@ -4748,7 +4747,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="2" spans="1:39" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>39763702</v>
       </c>
@@ -4860,7 +4859,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="3" spans="1:39" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>39781256</v>
       </c>
@@ -4976,7 +4975,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="4" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>39824916</v>
       </c>
@@ -5089,7 +5088,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="5" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>39829083</v>
       </c>
@@ -5206,7 +5205,7 @@
       </c>
       <c r="AM5"/>
     </row>
-    <row r="6" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>39885183</v>
       </c>
@@ -5300,7 +5299,7 @@
       <c r="AL6"/>
       <c r="AM6"/>
     </row>
-    <row r="7" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>40073143</v>
       </c>
@@ -5405,7 +5404,7 @@
       </c>
       <c r="AM7"/>
     </row>
-    <row r="8" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>40157991</v>
       </c>
@@ -5508,7 +5507,7 @@
       <c r="AL8"/>
       <c r="AM8"/>
     </row>
-    <row r="9" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>40185870</v>
       </c>
@@ -5613,7 +5612,7 @@
       </c>
       <c r="AM9"/>
     </row>
-    <row r="10" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>40235724</v>
       </c>
@@ -5709,7 +5708,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="11" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>40249821</v>
       </c>
@@ -5803,7 +5802,7 @@
       <c r="AL11"/>
       <c r="AM11"/>
     </row>
-    <row r="12" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>40267070</v>
       </c>
@@ -6036,7 +6035,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="14" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>40313383</v>
       </c>
@@ -6150,7 +6149,7 @@
       </c>
       <c r="AM14"/>
     </row>
-    <row r="15" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>40328893</v>
       </c>
@@ -6244,7 +6243,7 @@
       <c r="AL15"/>
       <c r="AM15"/>
     </row>
-    <row r="16" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>40332859</v>
       </c>
@@ -6355,7 +6354,7 @@
       </c>
       <c r="AM16"/>
     </row>
-    <row r="17" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>40342697</v>
       </c>
@@ -6449,7 +6448,7 @@
       <c r="AL17"/>
       <c r="AM17"/>
     </row>
-    <row r="18" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>40365478</v>
       </c>
@@ -6547,7 +6546,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="19" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>40373086</v>
       </c>
@@ -6641,7 +6640,7 @@
       <c r="AL19"/>
       <c r="AM19"/>
     </row>
-    <row r="20" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>40440280</v>
       </c>
@@ -6735,7 +6734,7 @@
       <c r="AL20"/>
       <c r="AM20"/>
     </row>
-    <row r="21" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>40442179</v>
       </c>
@@ -6846,7 +6845,7 @@
       </c>
       <c r="AM21"/>
     </row>
-    <row r="22" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>40442238</v>
       </c>
@@ -6940,7 +6939,7 @@
       <c r="AL22"/>
       <c r="AM22"/>
     </row>
-    <row r="23" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>40491540</v>
       </c>
@@ -7059,7 +7058,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="24" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>40498736</v>
       </c>
@@ -7172,7 +7171,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="25" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>40533559</v>
       </c>
@@ -7269,7 +7268,7 @@
       <c r="AL25"/>
       <c r="AM25"/>
     </row>
-    <row r="26" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>40544360</v>
       </c>
@@ -7380,7 +7379,7 @@
       </c>
       <c r="AM26"/>
     </row>
-    <row r="27" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>40577275</v>
       </c>
@@ -7474,7 +7473,7 @@
       <c r="AL27"/>
       <c r="AM27"/>
     </row>
-    <row r="28" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>40594860</v>
       </c>
@@ -7568,7 +7567,7 @@
       <c r="AL28"/>
       <c r="AM28"/>
     </row>
-    <row r="29" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>40610581</v>
       </c>
@@ -7665,7 +7664,7 @@
       <c r="AL29"/>
       <c r="AM29"/>
     </row>
-    <row r="30" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>40625334</v>
       </c>
@@ -7782,7 +7781,7 @@
       </c>
       <c r="AM30"/>
     </row>
-    <row r="31" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>40680123</v>
       </c>
@@ -7876,7 +7875,7 @@
       <c r="AL31"/>
       <c r="AM31"/>
     </row>
-    <row r="32" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>40702040</v>
       </c>
@@ -7989,7 +7988,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="33" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>40707527</v>
       </c>
@@ -8083,7 +8082,7 @@
       <c r="AL33"/>
       <c r="AM33"/>
     </row>
-    <row r="34" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>40708623</v>
       </c>
@@ -8202,7 +8201,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="35" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>40748179</v>
       </c>
@@ -8313,7 +8312,7 @@
       </c>
       <c r="AM35"/>
     </row>
-    <row r="36" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>40838887</v>
       </c>
@@ -8424,7 +8423,7 @@
       </c>
       <c r="AM36"/>
     </row>
-    <row r="37" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>40845075</v>
       </c>
@@ -8518,7 +8517,7 @@
       <c r="AL37"/>
       <c r="AM37"/>
     </row>
-    <row r="38" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>40936331</v>
       </c>
@@ -8629,7 +8628,7 @@
       </c>
       <c r="AM38"/>
     </row>
-    <row r="39" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>41062646</v>
       </c>
@@ -8726,7 +8725,7 @@
       <c r="AL39"/>
       <c r="AM39"/>
     </row>
-    <row r="40" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>41070939</v>
       </c>
@@ -8837,7 +8836,7 @@
       </c>
       <c r="AM40"/>
     </row>
-    <row r="41" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>41107300</v>
       </c>
@@ -8931,7 +8930,7 @@
       <c r="AL41"/>
       <c r="AM41"/>
     </row>
-    <row r="42" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41124262</v>
       </c>
@@ -9025,7 +9024,7 @@
       <c r="AL42"/>
       <c r="AM42"/>
     </row>
-    <row r="43" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41134770</v>
       </c>
@@ -9119,7 +9118,7 @@
       <c r="AL43"/>
       <c r="AM43"/>
     </row>
-    <row r="44" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>41173999</v>
       </c>
@@ -9236,7 +9235,7 @@
       </c>
       <c r="AM44"/>
     </row>
-    <row r="45" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>41206876</v>
       </c>
@@ -9353,7 +9352,7 @@
       </c>
       <c r="AM45"/>
     </row>
-    <row r="46" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>41250744</v>
       </c>
@@ -9470,7 +9469,7 @@
       </c>
       <c r="AM46"/>
     </row>
-    <row r="47" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>41302840</v>
       </c>
@@ -9581,7 +9580,7 @@
       </c>
       <c r="AM47"/>
     </row>
-    <row r="48" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>41309772</v>
       </c>
@@ -9675,7 +9674,7 @@
       <c r="AL48"/>
       <c r="AM48"/>
     </row>
-    <row r="49" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>986</v>
       </c>
@@ -9792,7 +9791,7 @@
       </c>
       <c r="AM49"/>
     </row>
-    <row r="50" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>987</v>
       </c>
@@ -9911,7 +9910,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="51" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>39775357</v>
       </c>
@@ -10030,7 +10029,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="52" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>38041538</v>
       </c>
@@ -10124,7 +10123,7 @@
       <c r="AL52"/>
       <c r="AM52"/>
     </row>
-    <row r="53" spans="1:39" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>38949049</v>
       </c>
@@ -10240,7 +10239,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="54" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>39221784</v>
       </c>
@@ -10333,7 +10332,7 @@
       </c>
       <c r="AM54"/>
     </row>
-    <row r="55" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>39530499</v>
       </c>
@@ -10429,7 +10428,7 @@
       </c>
       <c r="AM55"/>
     </row>
-    <row r="56" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>39558756</v>
       </c>
@@ -10522,7 +10521,7 @@
       </c>
       <c r="AM56"/>
     </row>
-    <row r="57" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>39605240</v>
       </c>
@@ -10615,7 +10614,7 @@
       </c>
       <c r="AM57"/>
     </row>
-    <row r="58" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>39618182</v>
       </c>
@@ -10720,7 +10719,7 @@
       </c>
       <c r="AM58"/>
     </row>
-    <row r="59" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>39664073</v>
       </c>
@@ -10837,7 +10836,7 @@
       </c>
       <c r="AM59"/>
     </row>
-    <row r="60" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>39698753</v>
       </c>
@@ -10932,7 +10931,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="61" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>39758026</v>
       </c>
@@ -11051,7 +11050,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="62" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>39800782</v>
       </c>
@@ -11167,7 +11166,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="63" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>39803200</v>
       </c>
@@ -11262,7 +11261,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="64" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>39816957</v>
       </c>
@@ -11378,7 +11377,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>39821144</v>
       </c>
@@ -11588,7 +11587,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="67" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>39824878</v>
       </c>
@@ -11823,7 +11822,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="69" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>39827291</v>
       </c>
@@ -11924,7 +11923,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="70" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>39843490</v>
       </c>
@@ -12018,7 +12017,7 @@
       <c r="AL70"/>
       <c r="AM70"/>
     </row>
-    <row r="71" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>39854398</v>
       </c>
@@ -12113,7 +12112,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="72" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>39854505</v>
       </c>
@@ -12229,7 +12228,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="73" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>39859647</v>
       </c>
@@ -12339,7 +12338,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="74" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>39888991</v>
       </c>
@@ -12432,7 +12431,7 @@
       </c>
       <c r="AM74"/>
     </row>
-    <row r="75" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>39891496</v>
       </c>
@@ -12549,7 +12548,7 @@
       </c>
       <c r="AM75" s="7"/>
     </row>
-    <row r="76" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>39896772</v>
       </c>
@@ -12665,7 +12664,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="77" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>39901891</v>
       </c>
@@ -12769,7 +12768,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="78" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>39919107</v>
       </c>
@@ -12870,7 +12869,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="79" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>39922881</v>
       </c>
@@ -12963,7 +12962,7 @@
       </c>
       <c r="AM79"/>
     </row>
-    <row r="80" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>39939372</v>
       </c>
@@ -13079,7 +13078,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="81" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>39951454</v>
       </c>
@@ -13195,7 +13194,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="82" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>39967439</v>
       </c>
@@ -13311,7 +13310,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="83" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>39993196</v>
       </c>
@@ -13421,7 +13420,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="84" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>40009682</v>
       </c>
@@ -13515,7 +13514,7 @@
       <c r="AL84"/>
       <c r="AM84"/>
     </row>
-    <row r="85" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>40060728</v>
       </c>
@@ -13628,7 +13627,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="86" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>40083728</v>
       </c>
@@ -13744,7 +13743,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="87" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>40083732</v>
       </c>
@@ -13860,7 +13859,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="88" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>40092896</v>
       </c>
@@ -13970,7 +13969,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="89" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>40098450</v>
       </c>
@@ -14080,7 +14079,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="90" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>40108247</v>
       </c>
@@ -14181,7 +14180,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="91" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>40108992</v>
       </c>
@@ -14282,7 +14281,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="92" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>40130004</v>
       </c>
@@ -14392,7 +14391,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="93" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>40163496</v>
       </c>
@@ -14484,7 +14483,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="94" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>40181915</v>
       </c>
@@ -14600,7 +14599,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="95" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>40184465</v>
       </c>
@@ -14692,7 +14691,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="96" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>40190799</v>
       </c>
@@ -14808,7 +14807,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="97" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>40192444</v>
       </c>
@@ -14903,7 +14902,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="98" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>40212919</v>
       </c>
@@ -15019,7 +15018,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="99" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>40225886</v>
       </c>
@@ -15114,7 +15113,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="100" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>40231377</v>
       </c>
@@ -15209,7 +15208,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="101" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>40233114</v>
       </c>
@@ -15304,7 +15303,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="102" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>40234759</v>
       </c>
@@ -15399,7 +15398,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="103" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>40247077</v>
       </c>
@@ -15515,7 +15514,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="104" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>40251217</v>
       </c>
@@ -15616,7 +15615,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="105" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>40256745</v>
       </c>
@@ -15711,7 +15710,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="106" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>40265750</v>
       </c>
@@ -15827,7 +15826,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="107" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>40267118</v>
       </c>
@@ -15946,7 +15945,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="108" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>40274918</v>
       </c>
@@ -16062,7 +16061,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="109" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>40289691</v>
       </c>
@@ -16157,7 +16156,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="110" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>40290389</v>
       </c>
@@ -16273,7 +16272,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="111" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>40294088</v>
       </c>
@@ -16365,7 +16364,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="112" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>40297851</v>
       </c>
@@ -16484,7 +16483,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="113" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>40299874</v>
       </c>
@@ -16600,7 +16599,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="114" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>40341276</v>
       </c>
@@ -16719,7 +16718,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="115" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>40342189</v>
       </c>
@@ -16835,7 +16834,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="116" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>40343087</v>
       </c>
@@ -16933,7 +16932,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="117" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>40344217</v>
       </c>
@@ -17049,7 +17048,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="118" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>40344636</v>
       </c>
@@ -17144,7 +17143,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="119" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>40354397</v>
       </c>
@@ -17245,7 +17244,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="120" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>40356059</v>
       </c>
@@ -17340,7 +17339,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="121" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>40367138</v>
       </c>
@@ -17453,7 +17452,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="122" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>40370341</v>
       </c>
@@ -17572,7 +17571,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="123" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>40370348</v>
       </c>
@@ -17688,7 +17687,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="124" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>40390244</v>
       </c>
@@ -17780,7 +17779,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="125" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>40399511</v>
       </c>
@@ -17896,7 +17895,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="126" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>40420276</v>
       </c>
@@ -18012,7 +18011,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="127" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>40424320</v>
       </c>
@@ -18104,7 +18103,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="128" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>40429208</v>
       </c>
@@ -18220,7 +18219,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="129" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>40440350</v>
       </c>
@@ -18339,7 +18338,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="130" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>40468043</v>
       </c>
@@ -18434,7 +18433,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="131" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>40510631</v>
       </c>
@@ -18529,7 +18528,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="132" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>40514396</v>
       </c>
@@ -18645,7 +18644,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="133" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>40519851</v>
       </c>
@@ -18758,7 +18757,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="134" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>40529335</v>
       </c>
@@ -18874,7 +18873,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="135" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>40549799</v>
       </c>
@@ -18990,7 +18989,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="136" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>40555800</v>
       </c>
@@ -19106,7 +19105,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="137" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>40556505</v>
       </c>
@@ -19222,7 +19221,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="138" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>40560830</v>
       </c>
@@ -19341,7 +19340,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="139" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>40569987</v>
       </c>
@@ -19460,7 +19459,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="140" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>40584002</v>
       </c>
@@ -19573,7 +19572,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="141" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>40584003</v>
       </c>
@@ -19692,7 +19691,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="142" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>40584679</v>
       </c>
@@ -19808,7 +19807,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="143" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>40590503</v>
       </c>
@@ -19921,7 +19920,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="144" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>40594654</v>
       </c>
@@ -20016,7 +20015,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="145" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>40596608</v>
       </c>
@@ -20108,7 +20107,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="146" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>40596875</v>
       </c>
@@ -20218,7 +20217,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="147" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>40599881</v>
       </c>
@@ -20450,7 +20449,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="149" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>40642328</v>
       </c>
@@ -20566,7 +20565,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="150" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>40661918</v>
       </c>
@@ -20670,7 +20669,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="151" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>40661920</v>
       </c>
@@ -20786,7 +20785,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="152" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>40671726</v>
       </c>
@@ -20902,7 +20901,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="153" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>40679145</v>
       </c>
@@ -21018,7 +21017,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="154" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>40691214</v>
       </c>
@@ -21134,7 +21133,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="155" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>40694117</v>
       </c>
@@ -21229,7 +21228,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="156" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>40700368</v>
       </c>
@@ -21345,7 +21344,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="157" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>40718698</v>
       </c>
@@ -21434,7 +21433,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="158" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>40727909</v>
       </c>
@@ -21523,7 +21522,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="159" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>40737396</v>
       </c>
@@ -21612,7 +21611,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="160" spans="1:38" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>40740802</v>
       </c>
@@ -21701,7 +21700,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>40743124</v>
       </c>
@@ -21790,7 +21789,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="162" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>40755888</v>
       </c>
@@ -21879,7 +21878,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="163" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>40773234</v>
       </c>
@@ -21968,7 +21967,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="164" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>40814073</v>
       </c>
@@ -22057,7 +22056,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="165" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>40823059</v>
       </c>
@@ -22146,7 +22145,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="166" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>40823060</v>
       </c>
@@ -22235,7 +22234,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>40836053</v>
       </c>
@@ -22324,7 +22323,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>40858616</v>
       </c>
@@ -22413,7 +22412,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>40877366</v>
       </c>
@@ -22502,7 +22501,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>40892732</v>
       </c>
@@ -22591,7 +22590,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>40896100</v>
       </c>
@@ -22680,7 +22679,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>40900727</v>
       </c>
@@ -22769,7 +22768,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>40904371</v>
       </c>
@@ -22858,7 +22857,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>40936356</v>
       </c>
@@ -22947,7 +22946,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>40949732</v>
       </c>
@@ -23036,7 +23035,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>40950783</v>
       </c>
@@ -23125,7 +23124,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>40950792</v>
       </c>
@@ -23214,7 +23213,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>40952238</v>
       </c>
@@ -23303,7 +23302,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="179" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>40967248</v>
       </c>
@@ -23392,7 +23391,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="180" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>40977098</v>
       </c>
@@ -23481,7 +23480,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="181" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>40979803</v>
       </c>
@@ -23570,7 +23569,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="182" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>40982383</v>
       </c>
@@ -23659,7 +23658,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="183" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>40988003</v>
       </c>
@@ -23748,7 +23747,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="184" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>40989563</v>
       </c>
@@ -23837,7 +23836,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="185" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>41009167</v>
       </c>
@@ -23926,7 +23925,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="186" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>41032509</v>
       </c>
@@ -24015,7 +24014,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="187" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>41039012</v>
       </c>
@@ -24104,7 +24103,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="188" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>41055984</v>
       </c>
@@ -24193,7 +24192,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="189" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>41059358</v>
       </c>
@@ -24282,7 +24281,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="190" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>41076580</v>
       </c>
@@ -24371,7 +24370,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="191" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>41084912</v>
       </c>
@@ -24460,7 +24459,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="192" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>41093920</v>
       </c>
@@ -24549,7 +24548,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="193" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>41104050</v>
       </c>
@@ -24638,7 +24637,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="194" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>41112765</v>
       </c>
@@ -24727,7 +24726,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="195" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>41120419</v>
       </c>
@@ -24816,7 +24815,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="196" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>41121975</v>
       </c>
@@ -24905,7 +24904,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="197" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>41132809</v>
       </c>
@@ -24994,7 +24993,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="198" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>41136510</v>
       </c>
@@ -25083,7 +25082,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="199" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>41140304</v>
       </c>
@@ -25172,7 +25171,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="200" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>41140313</v>
       </c>
@@ -25261,7 +25260,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="201" spans="1:29" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>41140314</v>
       </c>
@@ -25350,44 +25349,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="202" spans="1:29" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="203" spans="1:29" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="204" spans="1:29" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="205" spans="1:29" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="206" spans="1:29" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="207" spans="1:29" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="208" spans="1:29" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="209" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="210" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="211" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="212" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="213" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="214" hidden="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:AM214" xr:uid="{F3B8D15F-4FE6-BE4B-97F4-E8728CDE7A9F}">
-    <filterColumn colId="32">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="33">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="35">
-      <filters>
-        <filter val="y"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="36">
-      <filters>
-        <filter val="pearson"/>
-        <filter val="pearson_naïve"/>
-        <filter val="pearson_naïve (performance::check_overdispersion)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AM214" xr:uid="{F3B8D15F-4FE6-BE4B-97F4-E8728CDE7A9F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AM213">
     <sortCondition sortBy="cellColor" ref="A2:A213" dxfId="0"/>
   </sortState>
